--- a/outputs/marine_equipment/Вес_арматуры.xlsx
+++ b/outputs/marine_equipment/Вес_арматуры.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -716,467 +716,486 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="D15" s="6" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>сетка фильтра</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>кран</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D17" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>По диаметрам</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Диаметр</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Позиций</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Штук</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Вес, кг</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Вес, тонн</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>не указан</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>313</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>2062</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>2.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Ду3</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>313</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2062</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Ду6</t>
+          <t>Ду3</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду6</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>970</v>
+        <v>104</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>608</v>
+        <v>42</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.61</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>123</v>
+        <v>970</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>123</v>
+        <v>608</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.12</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду15</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>511</v>
+        <v>123</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>856</v>
+        <v>123</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.86</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>179</v>
+        <v>511</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>488</v>
+        <v>856</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.49</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>628</v>
+        <v>488</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>270</v>
+        <v>628</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.27</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3429</v>
+        <v>270</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3.43</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Ду60</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2</v>
+        <v>243</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>32</v>
+        <v>3429</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.03</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду60</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1633</v>
+        <v>32</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1.63</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>384</v>
+        <v>1633</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.38</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>4689</v>
+        <v>384</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>4.69</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3725</v>
+        <v>4689</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>3.73</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>665</v>
+        <v>3651</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.67</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Ду150</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>300</v>
+        <v>665</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду150</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>2060</v>
+        <v>300</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>2.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Ду250</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>4620</v>
+        <v>2060</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>4.62</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Ду300</t>
+          <t>Ду250</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>5400</v>
+        <v>4620</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>5.4</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>Ду300</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>Ду350</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="6" t="n">
+      <c r="B41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E41" s="7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1678,24 +1697,24 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
+          <t>Клапан проходной фланцевый сталь</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G15" s="10">
         <f>E15*F15</f>
@@ -1708,7 +1727,7 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -1723,19 +1742,19 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
+          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G16" s="10">
         <f>E16*F16</f>
@@ -1748,7 +1767,7 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -1763,19 +1782,19 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
+          <t>Клапан фланцевый проходной ДУ25 ???</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="10">
         <f>E17*F17</f>
@@ -1808,11 +1827,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ25 ???</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>5</v>
@@ -1843,19 +1862,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Клапан Пожарный фланцевый угловой Ду32</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" s="10">
         <f>E19*F19</f>
@@ -1868,7 +1887,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1907,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду32</t>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
@@ -1908,7 +1927,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -1928,11 +1947,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>7</v>
@@ -1968,11 +1987,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F22" s="10" t="n">
         <v>7</v>
@@ -1988,7 +2007,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -2008,11 +2027,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>7</v>
@@ -2048,7 +2067,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="E24" s="8" t="n">
@@ -2068,7 +2087,7 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2111,7 @@
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>7</v>
@@ -2128,11 +2147,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F26" s="10" t="n">
         <v>7</v>
@@ -2163,19 +2182,19 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G27" s="10">
         <f>E27*F27</f>
@@ -2208,11 +2227,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
+          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F28" s="10" t="n">
         <v>10</v>
@@ -2228,7 +2247,7 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -2248,11 +2267,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
+          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>10</v>
@@ -2288,11 +2307,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
+          <t>Клапан фланцевый угловой Ду40 Ру10</t>
         </is>
       </c>
       <c r="E30" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>10</v>
@@ -2308,7 +2327,7 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2347,7 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру10</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
@@ -2368,11 +2387,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="10" t="n">
         <v>10</v>
@@ -2388,7 +2407,7 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -2403,19 +2422,19 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G33" s="10">
         <f>E33*F33</f>
@@ -2428,7 +2447,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -2448,11 +2467,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>14</v>
@@ -2492,7 +2511,7 @@
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>14</v>
@@ -2532,7 +2551,7 @@
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>14</v>
@@ -2568,11 +2587,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>14</v>
@@ -2588,7 +2607,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -2608,11 +2627,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" s="10" t="n">
         <v>14</v>
@@ -2648,11 +2667,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>14</v>
@@ -2668,7 +2687,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -2728,11 +2747,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>14</v>
@@ -2748,7 +2767,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -2768,11 +2787,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
         </is>
       </c>
       <c r="E42" s="8" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F42" s="10" t="n">
         <v>14</v>
@@ -2788,7 +2807,7 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2827,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>14</v>
@@ -2848,11 +2867,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
+          <t>Клапан фланцевый проходной Ду50 Ру25</t>
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
         <v>14</v>
@@ -2868,7 +2887,7 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -2888,11 +2907,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру25</t>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>14</v>
@@ -2908,7 +2927,7 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2947,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
       <c r="E46" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
         <v>14</v>
@@ -2948,7 +2967,7 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -2968,11 +2987,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+          <t>Клапан фланцевый угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F47" s="10" t="n">
         <v>14</v>
@@ -2988,7 +3007,7 @@
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3003,19 +3022,19 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50 Ру25</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
         </is>
       </c>
       <c r="E48" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G48" s="10">
         <f>E48*F48</f>
@@ -3048,11 +3067,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>20</v>
@@ -3068,7 +3087,7 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3088,11 +3107,11 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="E50" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="10" t="n">
         <v>20</v>
@@ -3108,7 +3127,7 @@
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -3128,11 +3147,11 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>20</v>
@@ -3168,7 +3187,7 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
         </is>
       </c>
       <c r="E52" s="8" t="n">
@@ -3208,11 +3227,11 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+          <t>Клапан фланцевый проходной Ду65</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>20</v>
@@ -3228,7 +3247,7 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3248,11 +3267,11 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65</t>
+          <t>Клапан фланцевый проходной Ду65 Ру10</t>
         </is>
       </c>
       <c r="E54" s="8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F54" s="10" t="n">
         <v>20</v>
@@ -3288,11 +3307,11 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F55" s="10" t="n">
         <v>20</v>
@@ -3332,7 +3351,7 @@
         </is>
       </c>
       <c r="E56" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F56" s="10" t="n">
         <v>20</v>
@@ -3372,7 +3391,7 @@
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>20</v>
@@ -3403,19 +3422,19 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
         </is>
       </c>
       <c r="E58" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G58" s="10">
         <f>E58*F58</f>
@@ -3428,7 +3447,7 @@
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3467,11 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
+          <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>23</v>
@@ -3468,7 +3487,7 @@
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3511,7 @@
         </is>
       </c>
       <c r="E60" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F60" s="10" t="n">
         <v>23</v>
@@ -3523,19 +3542,19 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду70 Ру10</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G61" s="10">
         <f>E61*F61</f>
@@ -3548,7 +3567,7 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3568,11 +3587,11 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
+          <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
         </is>
       </c>
       <c r="E62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="10" t="n">
         <v>28</v>
@@ -3588,7 +3607,7 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -3608,11 +3627,11 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
+          <t>Клапан фланцевый проходной Ду80</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>28</v>
@@ -3628,7 +3647,7 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3667,11 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80</t>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
         </is>
       </c>
       <c r="E64" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F64" s="10" t="n">
         <v>28</v>
@@ -3668,7 +3687,7 @@
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3707,7 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
@@ -3728,11 +3747,11 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
+          <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
       <c r="E66" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F66" s="10" t="n">
         <v>28</v>
@@ -3748,7 +3767,7 @@
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3763,19 +3782,19 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Клапан фланцевый проходной Ду100 Ру10</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G67" s="10">
         <f>E67*F67</f>
@@ -3808,11 +3827,11 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду100 Ру10</t>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
         </is>
       </c>
       <c r="E68" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F68" s="10" t="n">
         <v>40</v>
@@ -3828,7 +3847,7 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -3848,11 +3867,11 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>40</v>
@@ -3868,7 +3887,7 @@
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -3883,19 +3902,19 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
+          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
         </is>
       </c>
       <c r="E70" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G70" s="10">
         <f>E70*F70</f>
@@ -3928,11 +3947,11 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>55</v>
@@ -3948,7 +3967,7 @@
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -3968,11 +3987,11 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Клапан фланцевый проходной Ду125 Ру10</t>
         </is>
       </c>
       <c r="E72" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F72" s="10" t="n">
         <v>55</v>
@@ -4008,11 +4027,11 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>55</v>
@@ -4028,7 +4047,7 @@
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -4043,19 +4062,19 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду150</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+          <t>Клапан фланцевый проходной Ду150</t>
         </is>
       </c>
       <c r="E74" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G74" s="10">
         <f>E74*F74</f>
@@ -4068,7 +4087,7 @@
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4088,11 +4107,11 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду150</t>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>75</v>
@@ -4163,19 +4182,19 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Ду150</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="G77" s="10">
         <f>E77*F77</f>
@@ -4188,7 +4207,7 @@
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -4208,11 +4227,11 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Клапан фланцевый проходной Ду200 Ру6</t>
         </is>
       </c>
       <c r="E78" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F78" s="10" t="n">
         <v>130</v>
@@ -4228,7 +4247,7 @@
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4238,24 +4257,24 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200 Ру6</t>
+          <t>Клапан для манометра штуцерный сальниковый</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="G79" s="10">
         <f>E79*F79</f>
@@ -4268,7 +4287,7 @@
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -4288,11 +4307,11 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Клапан для манометра штуцерный сальниковый</t>
+          <t>Клапан дроссельный угловой штуцерный</t>
         </is>
       </c>
       <c r="E80" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F80" s="10" t="n">
         <v>2</v>
@@ -4308,7 +4327,7 @@
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4347,7 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
@@ -4368,11 +4387,11 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+          <t>Клапан штуцерный угловой Рр150/10</t>
         </is>
       </c>
       <c r="E82" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F82" s="10" t="n">
         <v>2</v>
@@ -4403,19 +4422,19 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>Ду3</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
+          <t>Клапан для манометра штущерный Ду3Ру400 новый</t>
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="G83" s="10">
         <f>E83*F83</f>
@@ -4443,19 +4462,19 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Ду3</t>
+          <t>Ду6</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный Ду3Ру400 новый</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
         </is>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G84" s="10">
         <f>E84*F84</f>
@@ -4528,11 +4547,11 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
         </is>
       </c>
       <c r="E86" s="8" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F86" s="10" t="n">
         <v>0.4</v>
@@ -4568,11 +4587,11 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0.4</v>
@@ -4608,11 +4627,11 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
       <c r="E88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="10" t="n">
         <v>0.4</v>
@@ -4648,11 +4667,11 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="10" t="n">
         <v>0.4</v>
@@ -4688,11 +4707,11 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+          <t>Клапан штуцерный угловой Ду6Ру100</t>
         </is>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="10" t="n">
         <v>0.4</v>
@@ -4723,19 +4742,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Ду6</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду6Ру100</t>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G91" s="10">
         <f>E91*F91</f>
@@ -4768,11 +4787,11 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
         </is>
       </c>
       <c r="E92" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F92" s="10" t="n">
         <v>0.6</v>
@@ -4808,7 +4827,7 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
@@ -4848,7 +4867,7 @@
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="E94" s="8" t="n">
@@ -4928,11 +4947,11 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="F96" s="10" t="n">
         <v>0.6</v>
@@ -4948,7 +4967,7 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4991,7 @@
         </is>
       </c>
       <c r="E97" s="8" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>0.6</v>
@@ -4988,7 +5007,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5027,7 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="E98" s="8" t="n">
@@ -5052,7 +5071,7 @@
         </is>
       </c>
       <c r="E99" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0.6</v>
@@ -5088,11 +5107,11 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="E100" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F100" s="10" t="n">
         <v>0.6</v>
@@ -5108,7 +5127,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5151,7 @@
         </is>
       </c>
       <c r="E101" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0.6</v>
@@ -5172,7 +5191,7 @@
         </is>
       </c>
       <c r="E102" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F102" s="10" t="n">
         <v>0.6</v>
@@ -5188,7 +5207,7 @@
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5231,7 @@
         </is>
       </c>
       <c r="E103" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>0.6</v>
@@ -5292,7 +5311,7 @@
         </is>
       </c>
       <c r="E105" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>0.6</v>
@@ -5332,7 +5351,7 @@
         </is>
       </c>
       <c r="E106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="10" t="n">
         <v>0.6</v>
@@ -5372,7 +5391,7 @@
         </is>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="10" t="n">
         <v>0.6</v>
@@ -5408,7 +5427,7 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
         </is>
       </c>
       <c r="E108" s="8" t="n">
@@ -5428,7 +5447,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -5448,11 +5467,11 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F109" s="10" t="n">
         <v>0.6</v>
@@ -5488,11 +5507,11 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру40 (СУНДУК)</t>
         </is>
       </c>
       <c r="E110" s="8" t="n">
-        <v>18</v>
+        <v>798</v>
       </c>
       <c r="F110" s="10" t="n">
         <v>0.6</v>
@@ -5508,7 +5527,7 @@
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -5528,11 +5547,11 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40 (СУНДУК)</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>798</v>
+        <v>1</v>
       </c>
       <c r="F111" s="10" t="n">
         <v>0.6</v>
@@ -5548,7 +5567,7 @@
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5591,7 @@
         </is>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="10" t="n">
         <v>0.6</v>
@@ -5608,11 +5627,11 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
         </is>
       </c>
       <c r="E113" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="10" t="n">
         <v>0.6</v>
@@ -5648,7 +5667,7 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
         </is>
       </c>
       <c r="E114" s="8" t="n">
@@ -5688,11 +5707,11 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F115" s="10" t="n">
         <v>0.6</v>
@@ -5732,7 +5751,7 @@
         </is>
       </c>
       <c r="E116" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F116" s="10" t="n">
         <v>0.6</v>
@@ -5768,11 +5787,11 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F117" s="10" t="n">
         <v>0.6</v>
@@ -5808,11 +5827,11 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="E118" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F118" s="10" t="n">
         <v>0.6</v>
@@ -5963,19 +5982,19 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду15</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="E122" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G122" s="10">
         <f>E122*F122</f>
@@ -6008,7 +6027,7 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
@@ -6028,7 +6047,7 @@
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -6088,11 +6107,11 @@
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="10" t="n">
         <v>1</v>
@@ -6132,7 +6151,7 @@
         </is>
       </c>
       <c r="E126" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="10" t="n">
         <v>1</v>
@@ -6168,11 +6187,11 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="10" t="n">
         <v>1</v>
@@ -6212,7 +6231,7 @@
         </is>
       </c>
       <c r="E128" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="10" t="n">
         <v>1</v>
@@ -6248,7 +6267,7 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
@@ -6328,11 +6347,11 @@
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
         </is>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F131" s="10" t="n">
         <v>1</v>
@@ -6348,7 +6367,7 @@
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -6368,11 +6387,11 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="E132" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>1</v>
@@ -6388,7 +6407,7 @@
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -6408,11 +6427,11 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15</t>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
       <c r="E133" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F133" s="10" t="n">
         <v>1</v>
@@ -6428,7 +6447,7 @@
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6471,7 @@
         </is>
       </c>
       <c r="E134" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F134" s="10" t="n">
         <v>1</v>
@@ -6492,7 +6511,7 @@
         </is>
       </c>
       <c r="E135" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="10" t="n">
         <v>1</v>
@@ -6532,7 +6551,7 @@
         </is>
       </c>
       <c r="E136" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136" s="10" t="n">
         <v>1</v>
@@ -6612,7 +6631,7 @@
         </is>
       </c>
       <c r="E138" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F138" s="10" t="n">
         <v>1</v>
@@ -6648,11 +6667,11 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="10" t="n">
         <v>1</v>
@@ -6668,7 +6687,7 @@
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6727,7 @@
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -6728,11 +6747,11 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="E141" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F141" s="10" t="n">
         <v>1</v>
@@ -6772,7 +6791,7 @@
         </is>
       </c>
       <c r="E142" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F142" s="10" t="n">
         <v>1</v>
@@ -6812,7 +6831,7 @@
         </is>
       </c>
       <c r="E143" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F143" s="10" t="n">
         <v>1</v>
@@ -6848,11 +6867,11 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
         </is>
       </c>
       <c r="E144" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F144" s="10" t="n">
         <v>1</v>
@@ -6888,11 +6907,11 @@
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру40</t>
+          <t>Клапан штущерный проходной Ду15</t>
         </is>
       </c>
       <c r="E145" s="8" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="F145" s="10" t="n">
         <v>1</v>
@@ -6908,7 +6927,7 @@
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -6928,11 +6947,11 @@
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Клапан штущерный проходной Ду15</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
         </is>
       </c>
       <c r="E146" s="8" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F146" s="10" t="n">
         <v>1</v>
@@ -6948,7 +6967,7 @@
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -6963,19 +6982,19 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
         </is>
       </c>
       <c r="E147" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G147" s="10">
         <f>E147*F147</f>
@@ -7008,11 +7027,11 @@
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="E148" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="10" t="n">
         <v>1.5</v>
@@ -7048,11 +7067,11 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
         </is>
       </c>
       <c r="E149" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" s="10" t="n">
         <v>1.5</v>
@@ -7088,7 +7107,7 @@
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
       <c r="E150" s="8" t="n">
@@ -7128,11 +7147,11 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="E151" s="8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F151" s="10" t="n">
         <v>1.5</v>
@@ -7148,7 +7167,7 @@
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7191,7 @@
         </is>
       </c>
       <c r="E152" s="8" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F152" s="10" t="n">
         <v>1.5</v>
@@ -7188,7 +7207,7 @@
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7231,7 @@
         </is>
       </c>
       <c r="E153" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F153" s="10" t="n">
         <v>1.5</v>
@@ -7248,7 +7267,7 @@
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="E154" s="8" t="n">
@@ -7292,7 +7311,7 @@
         </is>
       </c>
       <c r="E155" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F155" s="10" t="n">
         <v>1.5</v>
@@ -7332,7 +7351,7 @@
         </is>
       </c>
       <c r="E156" s="8" t="n">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="F156" s="10" t="n">
         <v>1.5</v>
@@ -7372,7 +7391,7 @@
         </is>
       </c>
       <c r="E157" s="8" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="F157" s="10" t="n">
         <v>1.5</v>
@@ -7412,7 +7431,7 @@
         </is>
       </c>
       <c r="E158" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="10" t="n">
         <v>1.5</v>
@@ -7492,7 +7511,7 @@
         </is>
       </c>
       <c r="E160" s="8" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F160" s="10" t="n">
         <v>1.5</v>
@@ -7532,7 +7551,7 @@
         </is>
       </c>
       <c r="E161" s="8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F161" s="10" t="n">
         <v>1.5</v>
@@ -7572,7 +7591,7 @@
         </is>
       </c>
       <c r="E162" s="8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F162" s="10" t="n">
         <v>1.5</v>
@@ -7612,7 +7631,7 @@
         </is>
       </c>
       <c r="E163" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F163" s="10" t="n">
         <v>1.5</v>
@@ -7652,7 +7671,7 @@
         </is>
       </c>
       <c r="E164" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F164" s="10" t="n">
         <v>1.5</v>
@@ -7692,7 +7711,7 @@
         </is>
       </c>
       <c r="E165" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F165" s="10" t="n">
         <v>1.5</v>
@@ -7772,7 +7791,7 @@
         </is>
       </c>
       <c r="E167" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F167" s="10" t="n">
         <v>1.5</v>
@@ -7808,11 +7827,11 @@
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="E168" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F168" s="10" t="n">
         <v>1.5</v>
@@ -7852,7 +7871,7 @@
         </is>
       </c>
       <c r="E169" s="8" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="F169" s="10" t="n">
         <v>1.5</v>
@@ -7892,7 +7911,7 @@
         </is>
       </c>
       <c r="E170" s="8" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="F170" s="10" t="n">
         <v>1.5</v>
@@ -7972,7 +7991,7 @@
         </is>
       </c>
       <c r="E172" s="8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F172" s="10" t="n">
         <v>1.5</v>
@@ -8012,7 +8031,7 @@
         </is>
       </c>
       <c r="E173" s="8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F173" s="10" t="n">
         <v>1.5</v>
@@ -8052,7 +8071,7 @@
         </is>
       </c>
       <c r="E174" s="8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F174" s="10" t="n">
         <v>1.5</v>
@@ -8092,7 +8111,7 @@
         </is>
       </c>
       <c r="E175" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F175" s="10" t="n">
         <v>1.5</v>
@@ -8128,11 +8147,11 @@
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
         </is>
       </c>
       <c r="E176" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F176" s="10" t="n">
         <v>1.5</v>
@@ -8168,11 +8187,11 @@
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
       <c r="E177" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F177" s="10" t="n">
         <v>1.5</v>
@@ -8208,7 +8227,7 @@
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
       <c r="E178" s="8" t="n">
@@ -8228,7 +8247,7 @@
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8248,11 +8267,11 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру100</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="E179" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F179" s="10" t="n">
         <v>1.5</v>
@@ -8292,7 +8311,7 @@
         </is>
       </c>
       <c r="E180" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F180" s="10" t="n">
         <v>1.5</v>
@@ -8308,7 +8327,7 @@
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -8328,11 +8347,11 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="E181" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F181" s="10" t="n">
         <v>1.5</v>
@@ -8372,7 +8391,7 @@
         </is>
       </c>
       <c r="E182" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" s="10" t="n">
         <v>1.5</v>
@@ -8412,7 +8431,7 @@
         </is>
       </c>
       <c r="E183" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F183" s="10" t="n">
         <v>1.5</v>
@@ -8448,11 +8467,11 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="E184" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F184" s="10" t="n">
         <v>1.5</v>
@@ -8468,7 +8487,7 @@
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8488,11 +8507,11 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="E185" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F185" s="10" t="n">
         <v>1.5</v>
@@ -8528,11 +8547,11 @@
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
       <c r="E186" s="8" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="F186" s="10" t="n">
         <v>1.5</v>
@@ -8563,19 +8582,19 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
         </is>
       </c>
       <c r="E187" s="8" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G187" s="10">
         <f>E187*F187</f>
@@ -8608,11 +8627,11 @@
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="E188" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F188" s="10" t="n">
         <v>2.5</v>
@@ -8648,11 +8667,11 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
+          <t>Клапан педальный Ду25 Китай</t>
         </is>
       </c>
       <c r="E189" s="8" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="F189" s="10" t="n">
         <v>2.5</v>
@@ -8688,11 +8707,11 @@
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 Китай</t>
+          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
         </is>
       </c>
       <c r="E190" s="8" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F190" s="10" t="n">
         <v>2.5</v>
@@ -8708,7 +8727,7 @@
       </c>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8728,11 +8747,11 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="E191" s="8" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="F191" s="10" t="n">
         <v>2.5</v>
@@ -8748,7 +8767,7 @@
       </c>
       <c r="J191" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8831,7 @@
         </is>
       </c>
       <c r="E193" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F193" s="10" t="n">
         <v>2.5</v>
@@ -8828,7 +8847,7 @@
       </c>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -8848,11 +8867,11 @@
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
       <c r="E194" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F194" s="10" t="n">
         <v>2.5</v>
@@ -8868,7 +8887,7 @@
       </c>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8911,7 @@
         </is>
       </c>
       <c r="E195" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F195" s="10" t="n">
         <v>2.5</v>
@@ -8932,7 +8951,7 @@
         </is>
       </c>
       <c r="E196" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" s="10" t="n">
         <v>2.5</v>
@@ -8963,19 +8982,19 @@
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру100</t>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
         </is>
       </c>
       <c r="E197" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G197" s="10">
         <f>E197*F197</f>
@@ -8988,7 +9007,7 @@
       </c>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9008,11 +9027,11 @@
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
         </is>
       </c>
       <c r="E198" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F198" s="10" t="n">
         <v>3.5</v>
@@ -9028,7 +9047,7 @@
       </c>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9048,11 +9067,11 @@
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+          <t>Клапан штуцерный угловой Ду32</t>
         </is>
       </c>
       <c r="E199" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F199" s="10" t="n">
         <v>3.5</v>
@@ -9068,7 +9087,7 @@
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9088,11 +9107,11 @@
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32</t>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
       <c r="E200" s="8" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F200" s="10" t="n">
         <v>3.5</v>
@@ -9108,7 +9127,7 @@
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9151,7 @@
         </is>
       </c>
       <c r="E201" s="8" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F201" s="10" t="n">
         <v>3.5</v>
@@ -9172,7 +9191,7 @@
         </is>
       </c>
       <c r="E202" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F202" s="10" t="n">
         <v>3.5</v>
@@ -9208,11 +9227,11 @@
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+          <t>Клапан штуцерный угловой Ду32 Ру160</t>
         </is>
       </c>
       <c r="E203" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F203" s="10" t="n">
         <v>3.5</v>
@@ -9252,7 +9271,7 @@
         </is>
       </c>
       <c r="E204" s="8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F204" s="10" t="n">
         <v>3.5</v>
@@ -9288,11 +9307,11 @@
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру160</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="E205" s="8" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F205" s="10" t="n">
         <v>3.5</v>
@@ -9308,7 +9327,7 @@
       </c>
       <c r="J205" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9351,7 @@
         </is>
       </c>
       <c r="E206" s="8" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F206" s="10" t="n">
         <v>3.5</v>
@@ -9372,7 +9391,7 @@
         </is>
       </c>
       <c r="E207" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F207" s="10" t="n">
         <v>3.5</v>
@@ -9448,11 +9467,11 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="E209" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F209" s="10" t="n">
         <v>3.5</v>
@@ -9483,19 +9502,19 @@
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
       <c r="E210" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="G210" s="10">
         <f>E210*F210</f>
@@ -9508,7 +9527,7 @@
       </c>
       <c r="J210" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9528,11 +9547,11 @@
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
       <c r="E211" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F211" s="10" t="n">
         <v>7</v>
@@ -9548,7 +9567,7 @@
       </c>
       <c r="J211" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -9568,11 +9587,11 @@
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
       <c r="E212" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F212" s="10" t="n">
         <v>7</v>
@@ -9603,19 +9622,19 @@
       </c>
       <c r="C213" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
       <c r="E213" s="8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G213" s="10">
         <f>E213*F213</f>
@@ -9628,7 +9647,7 @@
       </c>
       <c r="J213" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9638,24 +9657,24 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клинкет/задвижка</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+          <t>Задвижки (желтая) ок. крышек</t>
         </is>
       </c>
       <c r="E214" s="8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G214" s="10">
         <f>E214*F214</f>
@@ -9688,11 +9707,11 @@
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>Задвижки (желтая) ок. крышек</t>
+          <t>Электропривод к задвижке</t>
         </is>
       </c>
       <c r="E215" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F215" s="10" t="n">
         <v>40</v>
@@ -9708,7 +9727,7 @@
       </c>
       <c r="J215" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9767,7 @@
       </c>
       <c r="J216" s="8" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>ЗИП и насосы</t>
         </is>
       </c>
     </row>
@@ -9763,19 +9782,19 @@
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
       <c r="E217" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G217" s="10">
         <f>E217*F217</f>
@@ -9788,7 +9807,7 @@
       </c>
       <c r="J217" s="8" t="inlineStr">
         <is>
-          <t>ЗИП и насосы</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -9803,19 +9822,19 @@
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду60</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="E218" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G218" s="10">
         <f>E218*F218</f>
@@ -9868,7 +9887,7 @@
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -9883,19 +9902,19 @@
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Ду60</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
+          <t>Задвижка клинкетная Ду65</t>
         </is>
       </c>
       <c r="E220" s="8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G220" s="10">
         <f>E220*F220</f>
@@ -9923,19 +9942,19 @@
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду65</t>
+          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
         </is>
       </c>
       <c r="E221" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G221" s="10">
         <f>E221*F221</f>
@@ -9963,19 +9982,19 @@
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
         </is>
       </c>
       <c r="E222" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G222" s="10">
         <f>E222*F222</f>
@@ -9988,7 +10007,7 @@
       </c>
       <c r="J222" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10008,11 +10027,11 @@
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная ДУ 80, сталь</t>
+          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
         </is>
       </c>
       <c r="E223" s="8" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F223" s="10" t="n">
         <v>28</v>
@@ -10048,11 +10067,11 @@
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 80 БРОНЗА</t>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
         </is>
       </c>
       <c r="E224" s="8" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F224" s="10" t="n">
         <v>28</v>
@@ -10088,11 +10107,11 @@
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
         </is>
       </c>
       <c r="E225" s="8" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F225" s="10" t="n">
         <v>28</v>
@@ -10108,7 +10127,7 @@
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10123,19 +10142,19 @@
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду80 Ру6</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="E226" s="8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G226" s="10">
         <f>E226*F226</f>
@@ -10148,7 +10167,7 @@
       </c>
       <c r="J226" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -10168,11 +10187,11 @@
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
+          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
         </is>
       </c>
       <c r="E227" s="8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F227" s="10" t="n">
         <v>45</v>
@@ -10188,7 +10207,7 @@
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10208,11 +10227,11 @@
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 100 БРОНЗА</t>
+          <t>Задвижка клинкетная Ду100</t>
         </is>
       </c>
       <c r="E228" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F228" s="10" t="n">
         <v>45</v>
@@ -10228,7 +10247,7 @@
       </c>
       <c r="J228" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10271,7 @@
         </is>
       </c>
       <c r="E229" s="8" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F229" s="10" t="n">
         <v>45</v>
@@ -10288,11 +10307,11 @@
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100</t>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
         </is>
       </c>
       <c r="E230" s="8" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F230" s="10" t="n">
         <v>45</v>
@@ -10308,7 +10327,7 @@
       </c>
       <c r="J230" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10328,11 +10347,11 @@
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+          <t>Клинкет Ду 100, сталь</t>
         </is>
       </c>
       <c r="E231" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F231" s="10" t="n">
         <v>45</v>
@@ -10348,7 +10367,7 @@
       </c>
       <c r="J231" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -10363,19 +10382,19 @@
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
+          <t>Клинкет Ду 200</t>
         </is>
       </c>
       <c r="E232" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="G232" s="10">
         <f>E232*F232</f>
@@ -10403,19 +10422,19 @@
       </c>
       <c r="C233" s="8" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду250</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Клинкет Ду 200</t>
+          <t>Задвижка клинкетная Ду 250</t>
         </is>
       </c>
       <c r="E233" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="G233" s="10">
         <f>E233*F233</f>
@@ -10428,7 +10447,7 @@
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10448,11 +10467,11 @@
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 250</t>
+          <t>Клинкет Ду 250</t>
         </is>
       </c>
       <c r="E234" s="8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F234" s="10" t="n">
         <v>220</v>
@@ -10468,7 +10487,7 @@
       </c>
       <c r="J234" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10507,7 @@
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Клинкет Ду 250</t>
+          <t>Клинкет Ду 250 не комплект</t>
         </is>
       </c>
       <c r="E235" s="8" t="n">
@@ -10523,19 +10542,19 @@
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Ду250</t>
+          <t>Ду300</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>Клинкет Ду 250 не комплект</t>
+          <t>Задвижка клинкетная стальная Ду300</t>
         </is>
       </c>
       <c r="E236" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="G236" s="10">
         <f>E236*F236</f>
@@ -10548,7 +10567,7 @@
       </c>
       <c r="J236" s="8" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10568,11 +10587,11 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная стальная Ду300</t>
+          <t>Клинкет Ду 300</t>
         </is>
       </c>
       <c r="E237" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F237" s="10" t="n">
         <v>300</v>
@@ -10588,7 +10607,7 @@
       </c>
       <c r="J237" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -10603,19 +10622,19 @@
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Ду300</t>
+          <t>Ду350</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>Клинкет Ду 300</t>
+          <t>Клинкет Ду 350</t>
         </is>
       </c>
       <c r="E238" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G238" s="10">
         <f>E238*F238</f>
@@ -10638,24 +10657,24 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>клинкет/задвижка</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>Ду350</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Клинкет Ду 350</t>
+          <t>Коробка 2-х клапанная корпус</t>
         </is>
       </c>
       <c r="E239" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="G239" s="10">
         <f>E239*F239</f>
@@ -10668,7 +10687,7 @@
       </c>
       <c r="J239" s="8" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10683,19 +10702,19 @@
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
       <c r="E240" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G240" s="10">
         <f>E240*F240</f>
@@ -10708,7 +10727,7 @@
       </c>
       <c r="J240" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10751,7 @@
         </is>
       </c>
       <c r="E241" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F241" s="10" t="n">
         <v>25</v>
@@ -10748,7 +10767,7 @@
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10768,11 +10787,11 @@
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="E242" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F242" s="10" t="n">
         <v>25</v>
@@ -10788,7 +10807,7 @@
       </c>
       <c r="J242" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10808,11 +10827,11 @@
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="E243" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F243" s="10" t="n">
         <v>25</v>
@@ -10828,7 +10847,7 @@
       </c>
       <c r="J243" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10871,7 @@
         </is>
       </c>
       <c r="E244" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F244" s="10" t="n">
         <v>25</v>
@@ -10883,19 +10902,19 @@
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="E245" s="8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G245" s="10">
         <f>E245*F245</f>
@@ -10908,7 +10927,7 @@
       </c>
       <c r="J245" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10951,7 @@
         </is>
       </c>
       <c r="E246" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F246" s="10" t="n">
         <v>45</v>
@@ -10948,7 +10967,7 @@
       </c>
       <c r="J246" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11031,7 @@
         </is>
       </c>
       <c r="E248" s="8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F248" s="10" t="n">
         <v>45</v>
@@ -11048,11 +11067,11 @@
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="E249" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F249" s="10" t="n">
         <v>45</v>
@@ -11068,7 +11087,7 @@
       </c>
       <c r="J249" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11111,7 @@
         </is>
       </c>
       <c r="E250" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F250" s="10" t="n">
         <v>45</v>
@@ -11108,7 +11127,7 @@
       </c>
       <c r="J250" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11128,11 +11147,11 @@
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
       <c r="E251" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F251" s="10" t="n">
         <v>45</v>
@@ -11172,7 +11191,7 @@
         </is>
       </c>
       <c r="E252" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F252" s="10" t="n">
         <v>45</v>
@@ -11203,19 +11222,19 @@
       </c>
       <c r="C253" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
       <c r="E253" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F253" s="10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G253" s="10">
         <f>E253*F253</f>
@@ -11228,7 +11247,7 @@
       </c>
       <c r="J253" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11238,24 +11257,24 @@
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>коробка клапанная</t>
+          <t>кран</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Коробка 3-х клап.фланцевая Ду100</t>
+          <t>Кран индикаторный VD26/20</t>
         </is>
       </c>
       <c r="E254" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F254" s="10" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="G254" s="10">
         <f>E254*F254</f>
@@ -11268,7 +11287,7 @@
       </c>
       <c r="J254" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11283,19 +11302,19 @@
       </c>
       <c r="C255" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Кран индикаторный VD26/20</t>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
       <c r="E255" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F255" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G255" s="10">
         <f>E255*F255</f>
@@ -11308,7 +11327,7 @@
       </c>
       <c r="J255" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11318,24 +11337,24 @@
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>кран</t>
+          <t>прочая арматура</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="E256" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F256" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G256" s="10">
         <f>E256*F256</f>
@@ -11368,7 +11387,7 @@
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="E257" s="8" t="n">
@@ -11408,11 +11427,11 @@
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Клапан ТНВД VD26/20</t>
         </is>
       </c>
       <c r="E258" s="8" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F258" s="10" t="n">
         <v>5</v>
@@ -11428,7 +11447,7 @@
       </c>
       <c r="J258" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11448,11 +11467,11 @@
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Клапан ТНВД VD26/20</t>
+          <t>Клапан всасывающий</t>
         </is>
       </c>
       <c r="E259" s="8" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F259" s="10" t="n">
         <v>5</v>
@@ -11468,7 +11487,7 @@
       </c>
       <c r="J259" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11488,11 +11507,11 @@
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Клапан всасывающий</t>
+          <t>Клапан выпускной 602-062-001</t>
         </is>
       </c>
       <c r="E260" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F260" s="10" t="n">
         <v>5</v>
@@ -11508,7 +11527,7 @@
       </c>
       <c r="J260" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11547,7 @@
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Клапан выпускной 602-062-001</t>
+          <t>Клапан выпускной 602-062-001-01</t>
         </is>
       </c>
       <c r="E261" s="8" t="n">
@@ -11568,11 +11587,11 @@
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Клапан выпускной 602-062-001-01</t>
+          <t>Клапан выхлопной</t>
         </is>
       </c>
       <c r="E262" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F262" s="10" t="n">
         <v>5</v>
@@ -11588,7 +11607,7 @@
       </c>
       <c r="J262" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11608,11 +11627,11 @@
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Клапан выхлопной</t>
+          <t>Клапан газораспредел. VD26/20 б/у</t>
         </is>
       </c>
       <c r="E263" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F263" s="10" t="n">
         <v>5</v>
@@ -11628,7 +11647,7 @@
       </c>
       <c r="J263" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11648,11 +11667,11 @@
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Клапан газораспредел. VD26/20 б/у</t>
+          <t>Клапан газораспределения</t>
         </is>
       </c>
       <c r="E264" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F264" s="10" t="n">
         <v>5</v>
@@ -11688,11 +11707,11 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Клапан газораспределения</t>
+          <t>Клапан компресс. ЭКП 70/25</t>
         </is>
       </c>
       <c r="E265" s="8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F265" s="10" t="n">
         <v>5</v>
@@ -11708,7 +11727,7 @@
       </c>
       <c r="J265" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11728,11 +11747,11 @@
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Клапан компресс. ЭКП 70/25</t>
+          <t>Клапан нагнетательный</t>
         </is>
       </c>
       <c r="E266" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F266" s="10" t="n">
         <v>5</v>
@@ -11768,11 +11787,11 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Клапан нагнетательный</t>
+          <t>Клапан нагнетательный ТНВД</t>
         </is>
       </c>
       <c r="E267" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F267" s="10" t="n">
         <v>5</v>
@@ -11788,7 +11807,7 @@
       </c>
       <c r="J267" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11808,11 +11827,11 @@
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Клапан нагнетательный ТНВД</t>
+          <t>Клапан пусковой</t>
         </is>
       </c>
       <c r="E268" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F268" s="10" t="n">
         <v>5</v>
@@ -11828,7 +11847,7 @@
       </c>
       <c r="J268" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11867,7 @@
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Клапан пусковой</t>
+          <t>Клапан пусковой главный</t>
         </is>
       </c>
       <c r="E269" s="8" t="n">
@@ -11868,7 +11887,7 @@
       </c>
       <c r="J269" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -11888,11 +11907,11 @@
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Клапан пусковой главный</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="E270" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F270" s="10" t="n">
         <v>5</v>
@@ -11908,7 +11927,7 @@
       </c>
       <c r="J270" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11928,11 +11947,11 @@
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
+          <t>Клапан электромагнитный б/у</t>
         </is>
       </c>
       <c r="E271" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F271" s="10" t="n">
         <v>5</v>
@@ -11948,7 +11967,7 @@
       </c>
       <c r="J271" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11968,11 +11987,11 @@
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
+          <t>Корпус выхлопного клапана</t>
         </is>
       </c>
       <c r="E272" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F272" s="10" t="n">
         <v>5</v>
@@ -12008,11 +12027,11 @@
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Корпус выхлопного клапана</t>
+          <t>Направляющая клапана</t>
         </is>
       </c>
       <c r="E273" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F273" s="10" t="n">
         <v>5</v>
@@ -12048,11 +12067,11 @@
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Направляющая клапана</t>
+          <t>Направляющий клапан (большой)</t>
         </is>
       </c>
       <c r="E274" s="8" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F274" s="10" t="n">
         <v>5</v>
@@ -12068,7 +12087,7 @@
       </c>
       <c r="J274" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -12088,11 +12107,11 @@
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Направляющий клапан (большой)</t>
+          <t>Направляющий клапан (маленький)</t>
         </is>
       </c>
       <c r="E275" s="8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F275" s="10" t="n">
         <v>5</v>
@@ -12128,11 +12147,11 @@
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Направляющий клапан (маленький)</t>
+          <t>Пружина клапана VD26/20</t>
         </is>
       </c>
       <c r="E276" s="8" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F276" s="10" t="n">
         <v>5</v>
@@ -12168,11 +12187,11 @@
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Пружина клапана VD26/20</t>
+          <t>Пружина клапана распределения наружная</t>
         </is>
       </c>
       <c r="E277" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F277" s="10" t="n">
         <v>5</v>
@@ -12208,11 +12227,11 @@
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Пружина клапана распределения наружная</t>
+          <t>Пружина нагнетательного клапана VD26/20</t>
         </is>
       </c>
       <c r="E278" s="8" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F278" s="10" t="n">
         <v>5</v>
@@ -12248,7 +12267,7 @@
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Пружина нагнетательного клапана VD26/20</t>
+          <t>Пружина нагнетательного клапана ТНВД</t>
         </is>
       </c>
       <c r="E279" s="8" t="n">
@@ -12288,11 +12307,11 @@
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Пружина нагнетательного клапана ТНВД</t>
+          <t>Седло впускного клапана</t>
         </is>
       </c>
       <c r="E280" s="8" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F280" s="10" t="n">
         <v>5</v>
@@ -12328,7 +12347,7 @@
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Седло впускного клапана</t>
+          <t>Седло клапана</t>
         </is>
       </c>
       <c r="E281" s="8" t="n">
@@ -12348,7 +12367,7 @@
       </c>
       <c r="J281" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -12368,11 +12387,11 @@
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Седло клапана</t>
+          <t>Судовая запорная арматура</t>
         </is>
       </c>
       <c r="E282" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F282" s="10" t="n">
         <v>5</v>
@@ -12388,7 +12407,7 @@
       </c>
       <c r="J282" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12408,11 +12427,11 @@
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
+          <t>Тарелка пружины клапана</t>
         </is>
       </c>
       <c r="E283" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F283" s="10" t="n">
         <v>5</v>
@@ -12428,7 +12447,7 @@
       </c>
       <c r="J283" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
@@ -12443,16 +12462,16 @@
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Тарелка пружины клапана</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="E284" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F284" s="10" t="n">
         <v>5</v>
@@ -12468,7 +12487,7 @@
       </c>
       <c r="J284" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12483,16 +12502,16 @@
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="E285" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F285" s="10" t="n">
         <v>5</v>
@@ -12528,11 +12547,11 @@
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="E286" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F286" s="10" t="n">
         <v>5</v>
@@ -12568,11 +12587,11 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="E287" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F287" s="10" t="n">
         <v>5</v>
@@ -12608,11 +12627,11 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
         </is>
       </c>
       <c r="E288" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F288" s="10" t="n">
         <v>5</v>
@@ -12643,16 +12662,16 @@
       </c>
       <c r="C289" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="E289" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F289" s="10" t="n">
         <v>5</v>
@@ -12683,16 +12702,16 @@
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="E290" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F290" s="10" t="n">
         <v>5</v>
@@ -12723,12 +12742,12 @@
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="E291" s="8" t="n">
@@ -12748,7 +12767,7 @@
       </c>
       <c r="J291" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -12758,24 +12777,24 @@
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>сетка фильтра</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
+          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
         </is>
       </c>
       <c r="E292" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F292" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G292" s="10">
         <f>E292*F292</f>
@@ -12788,7 +12807,7 @@
       </c>
       <c r="J292" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
